--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>70.5077938490504</v>
+        <v>11.45751650047069</v>
       </c>
       <c r="D2" t="n">
-        <v>64.68027403902721</v>
+        <v>10.51054453134192</v>
       </c>
       <c r="E2" t="n">
-        <v>7.550063319856982</v>
+        <v>1.226885289476759</v>
       </c>
       <c r="F2" t="n">
-        <v>8.706587517232521</v>
+        <v>1.414820471550284</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>85.60792048876436</v>
+        <v>13.91128707942421</v>
       </c>
       <c r="D3" t="n">
-        <v>82.09344907349225</v>
+        <v>13.34018547444249</v>
       </c>
       <c r="E3" t="n">
-        <v>7.550063319856982</v>
+        <v>1.226885289476759</v>
       </c>
       <c r="F3" t="n">
-        <v>8.706587517232521</v>
+        <v>1.414820471550284</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
